--- a/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
+++ b/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C491B9-5F87-FE4D-812E-AA664CB458F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984DCA1A-2F9F-2748-993D-889FFFC2AFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="1540" windowWidth="29260" windowHeight="16100" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>Det Value</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Soc Values</t>
   </si>
   <si>
-    <t>WDD</t>
-  </si>
-  <si>
     <t>Crime 0/+/-</t>
   </si>
   <si>
@@ -65,33 +62,6 @@
     <t>CCJ Funding (always on)</t>
   </si>
   <si>
-    <t>Detainee Low – No Crime Effect</t>
-  </si>
-  <si>
-    <t>Detainee Low – Crime Increases</t>
-  </si>
-  <si>
-    <t>Detainee Low – Crime Decreases</t>
-  </si>
-  <si>
-    <t>Detainee High – Community Effect – No Crime Effect</t>
-  </si>
-  <si>
-    <t>Detainee High – No Crime Effect (Baseline)</t>
-  </si>
-  <si>
-    <t>Detainee High – Community Effect – Crime Increases</t>
-  </si>
-  <si>
-    <t>Detainee High – Community Effect – Crime Decreases</t>
-  </si>
-  <si>
-    <t>Detainee High – Crime Increases</t>
-  </si>
-  <si>
-    <t>Detainee High – Crime Decreases</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -119,56 +89,98 @@
     <t>Pre-Trial Diversion</t>
   </si>
   <si>
-    <t>Bail Reform Scenario</t>
-  </si>
-  <si>
     <t>Policy Scenario Parameters 1</t>
   </si>
   <si>
-    <t>Policy Scenario Parameters 2</t>
-  </si>
-  <si>
     <t>Policy Scenario Parameters 3</t>
   </si>
   <si>
     <t>Max Detainee population (look at CCJ distribution 2005 -2025)</t>
   </si>
   <si>
-    <t>Bring back monetary bonds?</t>
-  </si>
-  <si>
     <t>Change Relative to Baseline</t>
   </si>
   <si>
-    <t>Alt Name / Natural Lang Label</t>
-  </si>
-  <si>
-    <t>Feedback:</t>
-  </si>
-  <si>
-    <t>The name should only map to the change from baseline, the main one should be the natural language name too (try chatgpt)</t>
-  </si>
-  <si>
-    <t>be clear about how this affects the numerator and denominator</t>
-  </si>
-  <si>
     <t>Haven</t>
   </si>
   <si>
     <t>Crime Cost</t>
   </si>
   <si>
-    <t>What happens to work, earnings, and tax revenue for people who would otherwise be detained? (include or ignore fiscal feedback from employment changes)</t>
-  </si>
-  <si>
-    <t>How much displacement is there? (if CCJ shrinks, what share of people end up jailed somewhere else)</t>
+    <t>Community effect (WDD)</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Assume Detention Increases Crime</t>
+  </si>
+  <si>
+    <t>Assume Detention Decreases Crime</t>
+  </si>
+  <si>
+    <t>Add Negative Spillover Effect on Community</t>
+  </si>
+  <si>
+    <t>Add Negative Spillover Effect on Community, Assume Detention Increases Crime</t>
+  </si>
+  <si>
+    <t>Add Negative Spillover Effect on Community, Assume Detention Decreases Crime</t>
+  </si>
+  <si>
+    <t>Alt Name</t>
+  </si>
+  <si>
+    <t>All scenarios include in the numerator a value to the detainee (negative) and a value for the effect on court appearance (positive). The denominator is always the 2018 Cook County Jail funding. The scenarios vary in the choice between two detainee values (both negative),  the inclusion of a value for the spillover effect of detention on the community (negative) in the  numerator, and  the inclusion of a crime effect assumption (negative or positive) which affects both the numerator and the denominator .</t>
+  </si>
+  <si>
+    <t>Baseline scenerio except the value of detention to detainees is measured by the WTP for Freedom instead of the Relative Harm Valuation (RHV). WTP for Freedom values detainee experience as roughly 300 times less negative than RHV, so this choice makes the numerator much less negative and brings the MVPF closer to 0 in the positive direction.</t>
+  </si>
+  <si>
+    <t>Less Negative Detainee Value</t>
+  </si>
+  <si>
+    <t>Less Negative Detainee Value, Assume Detention Increases Crime</t>
+  </si>
+  <si>
+    <t>Less Negative Detainee Value, Assume Detention Decreases Crime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The baseline scenario uses the components we feel are most defensible for inclusion based on literature backing and the desire to minimize necessary assumptions. We chose the Relative Harm Valuation as our detainee value, choose not to include community spillover effects, and set the crime effect equal to zero. </t>
+  </si>
+  <si>
+    <t>Same as the Baseline scenario, with the addition of an assumption that detention has an increasing effect on crime. This assumption adds a negative value to the numerator to reflect the effect of less crime on society, and decreases the cost to government in the denominator. The overall effect is __</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the Baseline scenario, with the addition of an assumption that detention has an decreasing effect on crime. This assumption adds a positive value to the numerator to reflect the ffect of that crime on society, and increases the cost to government in the denominator. The overall effect is __ . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crime effects value </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This scenerio adds a value to the numerator that captures some of the potential spillover effects of detention on the community of the detainee that are not already captured by the detainee value. This addition makes the numerator, and the overall MVPF, more negative. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the "Add Negative Spillover Effect on Community" scenario, with the addition of an assumption that detention has an decreasing effect on crime. This assumption adds a positive value to the numerator to reflect the ffect of that crime on society, and increases the cost to government in the denominator. The overall effect relative to the baseine MVPF is mixed, because the community value pulls it more negative, while the decreased crime assumption makes it more positive. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the "Add Negative Spillover Effect on Community" scenario, with the addition of an assumption that detention has an increasing effect on crime. This assumption adds a negative value to the numerator to reflect the effect of less crime on society, and decreases the cost to government in the denominator. The overall effect on the MVPF is negative, due to both the addition of the negative community value and the effects of increased crime. This scenario produces the most negative MVPF values of all of the available options. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the "Less Negative Detainee Value" scenario, with the addition of an assumption that detention has an increasing effect on crime. This assumption adds a negative value to the numerator to reflect the effect of less crime on society, and decreases the cost to government in the denominator. The overall effect relative to the baseine MVPF is mixed, because using the less negative detainee value pulls it closer to 0, while the increased crime assumption makes it more negative. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as the "Less Negative Detainee Value" scenario, with the addition of an assumption that detention has an decreasing effect on crime. This assumption adds a positive value to the numerator to reflect the ffect of that crime on society, and increases the cost to government in the denominator. The overall effect on the MVPF is positive (pulls closer to 0), due to both the use of the less negative detainee value and the positive effects of decreased crime. This scenario produces the most positive MVPF values of all of the available options. </t>
+  </si>
+  <si>
+    <t>Header text above scenerio selection</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -196,6 +208,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -217,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -233,6 +251,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,22 +589,23 @@
   <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="54.5" customWidth="1"/>
+    <col min="1" max="1" width="76.5" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="27.5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="15.83203125" customWidth="1"/>
     <col min="10" max="10" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>33</v>
+      <c r="A1" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -594,397 +614,406 @@
         <v>3</v>
       </c>
       <c r="J1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="L3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="C16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="6"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
+    <row r="23" spans="3:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
+++ b/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984DCA1A-2F9F-2748-993D-889FFFC2AFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACD4EE0-BD56-204A-9E9D-5AF786977C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="1540" windowWidth="29260" windowHeight="16100" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
   <si>
     <t>Det Value</t>
   </si>
@@ -174,13 +174,202 @@
   </si>
   <si>
     <t>Header text above scenerio selection</t>
+  </si>
+  <si>
+    <t>Header text above scenario selection</t>
+  </si>
+  <si>
+    <t>Most Conservative</t>
+  </si>
+  <si>
+    <t>Same components as the baseline, except the detainee value uses WTP for Freedom instead of RHV. Because WTP is much smaller in magnitude, the numerator is much less negative and the MVPF moves closer to zero.</t>
+  </si>
+  <si>
+    <t>Same as the Less Negative Detainee Value scenario, plus an assumption that detention increases crime. This adds a negative crime term to the numerator and increases government costs in the denominator. The WTP choice pushes the MVPF up, while the increased crime term pushes it down, so the net effect depends on their relative size.</t>
+  </si>
+  <si>
+    <t>Highest MVPF</t>
+  </si>
+  <si>
+    <t>Same as the Less Negative Detainee Value scenario, plus an assumption that detention decreases crime. This adds a positive crime term to the numerator and reduces government costs in the denominator. This combination tends to produce the highest (least negative) MVPF values.</t>
+  </si>
+  <si>
+    <t>Uses the components we view as most defensible: RHV for detainees, no community spillover term, and zero crime effect. This is the central estimate with the fewest additional assumptions.</t>
+  </si>
+  <si>
+    <t>Same as the baseline scenario, plus an assumption that detention increases crime. This adds a negative crime term to the numerator and increases government costs in the denominator, which tends to make the MVPF more negative than the baseline.</t>
+  </si>
+  <si>
+    <t>Same as the baseline scenario, plus an assumption that detention decreases crime. This adds a positive crime term to the numerator and reduces government costs in the denominator, which tends to make the MVPF less negative than the baseline.</t>
+  </si>
+  <si>
+    <t>This scenario adds a negative community spillover value to the numerator to capture harms to the detainee’s community not already counted. This makes the numerator more negative and lowers the MVPF.</t>
+  </si>
+  <si>
+    <t>Same as Add Negative Spillover Effect on Community, plus the increased crime assumption. The numerator becomes more negative and government costs rise, producing the lowest MVPF values.</t>
+  </si>
+  <si>
+    <t>Same as Add Negative Spillover Effect on Community, plus the decreased crime assumption. The community term pushes the MVPF downward, while the decreased crime term pushes it upward. The net effect relative to baseline depends on their relative size.</t>
+  </si>
+  <si>
+    <t>All scenarios include in the numerator a negative value to the detainee and a positive value for improved court appearance. The denominator always includes 2018 Cook County Jail funding. Scenarios differ by which detainee value is used, whether a negative community spillover term is added, and whether a crime effect (which affects both numerator and denominator) is included.</t>
+  </si>
+  <si>
+    <t>Lowest MVPF</t>
+  </si>
+  <si>
+    <t>One-sentence version</t>
+  </si>
+  <si>
+    <t>This scenario uses a smaller detainee harm estimate (WTP for Freedom instead of RHV), which makes the MVPF much less negative and closer to zero.</t>
+  </si>
+  <si>
+    <t>This scenario uses the smaller detainee harm estimate and assumes detention decreases crime, which together tend to produce the highest (least negative) MVPF values.</t>
+  </si>
+  <si>
+    <t>This scenario is the baseline, using RHV for detainees, no community spillover term, and no crime effect.</t>
+  </si>
+  <si>
+    <t>This scenario starts from the baseline and assumes detention increases crime, which tends to make the MVPF more negative than the baseline.</t>
+  </si>
+  <si>
+    <t>This scenario starts from the baseline and assumes detention decreases crime, which tends to make the MVPF less negative than the baseline.</t>
+  </si>
+  <si>
+    <t>This scenario adds a negative community spillover value to the baseline, making the MVPF more negative.</t>
+  </si>
+  <si>
+    <t>This scenario adds both the negative community spillover term and an increased-crime effect, tending to produce the lowest MVPF values.</t>
+  </si>
+  <si>
+    <t>This scenario adds the negative community spillover term and a decreased-crime effect, so the spillover pulls the MVPF down while the crime effect pushes it up.</t>
+  </si>
+  <si>
+    <t>This scenario uses the smaller detainee harm estimate and assumes detention increases crime. The detainee harm choice pushes the MVPF up while the crime effect pushes it down.</t>
+  </si>
+  <si>
+    <t>Normative Orientation</t>
+  </si>
+  <si>
+    <t>When You Might Choose This</t>
+  </si>
+  <si>
+    <t>All scenarios include in the numerator a negative value to the detainee and a positive value for improved court appearance. The denominator is always 2018 Cook County Jail funding. Scenarios differ by which detainee value is used, whether a negative community spillover term is added, and whether a crime effect is included.</t>
+  </si>
+  <si>
+    <t>Uses WTP instead of RHV, making the numerator less negative.</t>
+  </si>
+  <si>
+    <t>Assumes lower per-day detainee harm</t>
+  </si>
+  <si>
+    <t>Focus on conservative valuation of individual harms</t>
+  </si>
+  <si>
+    <t>Choose if you believe detainee harm should be valued using smaller, survey-based estimates</t>
+  </si>
+  <si>
+    <t>Uses WTP and assumes detention increases crime.</t>
+  </si>
+  <si>
+    <t>WTP harm + crime increase assumption</t>
+  </si>
+  <si>
+    <t>Focus on both conservative detainee valuation and possible criminogenic effects</t>
+  </si>
+  <si>
+    <t>Choose if you think detainee harm is lower but detention may increase crime</t>
+  </si>
+  <si>
+    <t>Uses WTP and assumes detention decreases crime.</t>
+  </si>
+  <si>
+    <t>WTP harm + crime decrease assumption</t>
+  </si>
+  <si>
+    <t>Focus on individual harm minimization and potential public safety benefits</t>
+  </si>
+  <si>
+    <t>Choose if you think detainee harm is smaller and detention may reduce crime</t>
+  </si>
+  <si>
+    <t>Uses RHV, no spillovers, and zero crime effect.</t>
+  </si>
+  <si>
+    <t>Assumes higher detainee harm and no broader spillovers</t>
+  </si>
+  <si>
+    <t>Focus on evidence-first minimal assumptions</t>
+  </si>
+  <si>
+    <t>Choose if you prefer sticking closely to the most supported and least assumptive components</t>
+  </si>
+  <si>
+    <t>Uses RHV and assumes detention increases crime.</t>
+  </si>
+  <si>
+    <t>RHV harm + crime increase assumption</t>
+  </si>
+  <si>
+    <t>Focus on individual harm plus potential criminogenic effects</t>
+  </si>
+  <si>
+    <t>Choose if you think detention may worsen public safety</t>
+  </si>
+  <si>
+    <t>Uses RHV and assumes detention decreases crime.</t>
+  </si>
+  <si>
+    <t>RHV harm + crime decrease assumption</t>
+  </si>
+  <si>
+    <t>Focus on individual harm plus potential public safety benefits</t>
+  </si>
+  <si>
+    <t>Choose if you think detention may reduce crime</t>
+  </si>
+  <si>
+    <t>Adds a negative community spillover term.</t>
+  </si>
+  <si>
+    <t>Assumes detention harms communities</t>
+  </si>
+  <si>
+    <t>Focus on broader social impact</t>
+  </si>
+  <si>
+    <t>Choose if you think detention produces wider community harms</t>
+  </si>
+  <si>
+    <t>Adds community spillover and assumes detention increases crime.</t>
+  </si>
+  <si>
+    <t>Community harm + crime increase assumption</t>
+  </si>
+  <si>
+    <t>Focus on broad social harms and criminogenic effects</t>
+  </si>
+  <si>
+    <t>Choose if you think detention harms both individuals and communities and may increase crime</t>
+  </si>
+  <si>
+    <t>Adds community spillover and assumes detention decreases crime.</t>
+  </si>
+  <si>
+    <t>Community harm + crime decrease assumption</t>
+  </si>
+  <si>
+    <t>Focus on community impacts with possible public safety benefits</t>
+  </si>
+  <si>
+    <t>Choose if you think detention harms communities but may reduce crime</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -214,6 +403,46 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -235,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -248,10 +477,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -586,133 +831,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE80E8B-CEB2-B84F-9C91-FD8EDADFF9F9}">
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="76.5" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="63" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="41.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="57.6640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="34" style="10" customWidth="1"/>
+    <col min="6" max="6" width="39.1640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:13" ht="25" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="300" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="200" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="275" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5">
@@ -721,112 +967,113 @@
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="325" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>-1</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
         <v>-1</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="200" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="200" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8">
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8">
@@ -835,109 +1082,109 @@
       <c r="J8">
         <v>1</v>
       </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="175" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>-1</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
         <v>-1</v>
       </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="175" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="300" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11">
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11">
@@ -946,49 +1193,52 @@
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="275" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
         <v>-1</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
         <v>-1</v>
       </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -996,24 +1246,361 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="50" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="C16" s="4" t="s">
+    <row r="16" spans="1:13" ht="25" x14ac:dyDescent="0.3">
+      <c r="D16" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="3:3" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="6"/>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="225" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="200" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="175" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="5" customFormat="1" ht="125" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="275" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" ht="100" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="100" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="100" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="75" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
+++ b/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/Spreadsheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACD4EE0-BD56-204A-9E9D-5AF786977C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9BDEC2-404C-5C46-BF0E-2BE19622701E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="1540" windowWidth="29260" windowHeight="16100" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17400" activeTab="1" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="109">
   <si>
     <t>Det Value</t>
   </si>
@@ -369,7 +370,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -395,20 +396,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -443,13 +430,63 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -464,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -473,30 +510,54 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -832,30 +893,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE80E8B-CEB2-B84F-9C91-FD8EDADFF9F9}">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="34" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="76.5" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="41.5" style="10" customWidth="1"/>
-    <col min="4" max="4" width="57.6640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="34" style="10" customWidth="1"/>
-    <col min="6" max="6" width="39.1640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="76.5" style="12" customWidth="1"/>
+    <col min="2" max="2" width="31" style="12" customWidth="1"/>
+    <col min="3" max="3" width="41.5" style="12" customWidth="1"/>
+    <col min="4" max="4" width="57.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="34" style="5" customWidth="1"/>
+    <col min="6" max="6" width="39.1640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="69.6640625" customWidth="1"/>
     <col min="10" max="10" width="15.83203125" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
@@ -865,21 +926,19 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="300" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="302" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -904,20 +963,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="200" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" ht="202" x14ac:dyDescent="0.4">
+      <c r="A4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="10">
-        <v>1</v>
-      </c>
-      <c r="F4" s="10">
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
         <v>0</v>
       </c>
       <c r="G4">
@@ -942,17 +1001,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="275" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" ht="277" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="10">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
         <v>0</v>
       </c>
       <c r="G5">
@@ -977,20 +1036,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="325" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" ht="327" x14ac:dyDescent="0.4">
+      <c r="A6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="10">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
         <v>0</v>
       </c>
       <c r="G6">
@@ -1015,21 +1074,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="200" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:13" ht="202" x14ac:dyDescent="0.4">
+      <c r="A7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="11" t="s">
+      <c r="C7" s="14"/>
+      <c r="D7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
         <v>1</v>
       </c>
       <c r="G7">
@@ -1054,20 +1113,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="200" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" ht="202" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
         <v>1</v>
       </c>
       <c r="G8">
@@ -1092,20 +1151,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="175" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" ht="177" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="10">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
         <v>1</v>
       </c>
       <c r="G9">
@@ -1130,17 +1189,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="175" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" ht="177" x14ac:dyDescent="0.4">
+      <c r="A10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
         <v>1</v>
       </c>
       <c r="G10">
@@ -1165,20 +1224,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="300" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" ht="302" x14ac:dyDescent="0.4">
+      <c r="A11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
         <v>1</v>
       </c>
       <c r="G11">
@@ -1203,17 +1262,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="275" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" ht="277" x14ac:dyDescent="0.4">
+      <c r="A12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="10">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
         <v>1</v>
       </c>
       <c r="G12">
@@ -1238,372 +1297,621 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="G13" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="50" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:13" ht="52" x14ac:dyDescent="0.4">
+      <c r="A15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="25" x14ac:dyDescent="0.3">
-      <c r="D16" s="11" t="s">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="D16" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="225" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:7" ht="227" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="125" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:7" ht="127" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="200" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:7" ht="202" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="175" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:7" ht="177" x14ac:dyDescent="0.4">
+      <c r="A22" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="5" customFormat="1" ht="125" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:7" s="4" customFormat="1" ht="127" x14ac:dyDescent="0.4">
+      <c r="A23" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-    </row>
-    <row r="24" spans="1:6" ht="150" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="1:7" ht="152" x14ac:dyDescent="0.4">
+      <c r="A24" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="150" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:7" ht="152" x14ac:dyDescent="0.4">
+      <c r="A25" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="125" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:7" ht="127" x14ac:dyDescent="0.4">
+      <c r="A26" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="125" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:7" ht="127" x14ac:dyDescent="0.4">
+      <c r="A27" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="150" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="28" spans="1:7" ht="152" x14ac:dyDescent="0.4">
+      <c r="A28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+    <row r="32" spans="1:7" s="3" customFormat="1" ht="23" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15" t="s">
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="16" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="275" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+      <c r="G32" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="230" x14ac:dyDescent="0.3">
+      <c r="A33" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="11" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-    </row>
-    <row r="34" spans="1:6" ht="100" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" spans="1:7" ht="140" x14ac:dyDescent="0.4">
+      <c r="A34" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="19" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="150" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+      <c r="G34" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="105" x14ac:dyDescent="0.4">
+      <c r="A35" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="11" t="s">
+      <c r="B35" s="15"/>
+      <c r="C35" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="125" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+    <row r="36" spans="1:7" ht="105" x14ac:dyDescent="0.4">
+      <c r="A36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="100" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+    <row r="37" spans="1:7" ht="105" x14ac:dyDescent="0.4">
+      <c r="A37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="19" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="125" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+      <c r="G37" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="105" x14ac:dyDescent="0.4">
+      <c r="A38" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="100" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+    <row r="39" spans="1:7" ht="105" x14ac:dyDescent="0.4">
+      <c r="A39" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="75" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
+    <row r="40" spans="1:7" ht="105" x14ac:dyDescent="0.4">
+      <c r="A40" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="11" t="s">
+      <c r="B40" s="15"/>
+      <c r="C40" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="125" x14ac:dyDescent="0.3">
-      <c r="A41" s="9" t="s">
+    <row r="41" spans="1:7" ht="140" x14ac:dyDescent="0.4">
+      <c r="A41" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="19" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="125" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="G41" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="140" x14ac:dyDescent="0.4">
+      <c r="A42" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="11" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="15"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13D4B0-48A1-0F49-921C-E1EA8DE8A107}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="32" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="6" width="46.83203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="103.5" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="66" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="27" customFormat="1" ht="90" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" ht="132" x14ac:dyDescent="0.4">
+      <c r="A3" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="132" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="132" x14ac:dyDescent="0.4">
+      <c r="A5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="132" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="99" x14ac:dyDescent="0.4">
+      <c r="A7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="99" x14ac:dyDescent="0.4">
+      <c r="A8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="99" x14ac:dyDescent="0.4">
+      <c r="A9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="165" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="132" x14ac:dyDescent="0.4">
+      <c r="A11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
+++ b/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/Spreadsheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9BDEC2-404C-5C46-BF0E-2BE19622701E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACD4EE0-BD56-204A-9E9D-5AF786977C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17400" activeTab="1" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
+    <workbookView xWindow="140" yWindow="1540" windowWidth="29260" windowHeight="16100" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
   <si>
     <t>Det Value</t>
   </si>
@@ -370,7 +369,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -396,6 +395,20 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -430,63 +443,13 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -501,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -510,54 +473,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,30 +832,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE80E8B-CEB2-B84F-9C91-FD8EDADFF9F9}">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="34" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="76.5" style="12" customWidth="1"/>
-    <col min="2" max="2" width="31" style="12" customWidth="1"/>
-    <col min="3" max="3" width="41.5" style="12" customWidth="1"/>
-    <col min="4" max="4" width="57.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="34" style="5" customWidth="1"/>
-    <col min="6" max="6" width="39.1640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="69.6640625" customWidth="1"/>
+    <col min="1" max="1" width="76.5" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="41.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="57.6640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="34" style="10" customWidth="1"/>
+    <col min="6" max="6" width="39.1640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="10" max="10" width="15.83203125" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:13" ht="25" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
@@ -926,19 +865,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="302" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="300" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -963,20 +904,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="202" x14ac:dyDescent="0.4">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:13" ht="200" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
         <v>0</v>
       </c>
       <c r="G4">
@@ -1001,17 +942,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="277" x14ac:dyDescent="0.4">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:13" ht="275" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>0</v>
       </c>
       <c r="G5">
@@ -1036,20 +977,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="327" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:13" ht="325" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
         <v>0</v>
       </c>
       <c r="G6">
@@ -1074,21 +1015,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="202" x14ac:dyDescent="0.4">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:13" ht="200" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
         <v>1</v>
       </c>
       <c r="G7">
@@ -1113,20 +1054,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="202" x14ac:dyDescent="0.4">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:13" ht="200" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
         <v>1</v>
       </c>
       <c r="G8">
@@ -1151,20 +1092,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="177" x14ac:dyDescent="0.4">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="175" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
         <v>1</v>
       </c>
       <c r="G9">
@@ -1189,17 +1130,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="177" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:13" ht="175" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
         <v>1</v>
       </c>
       <c r="G10">
@@ -1224,20 +1165,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="302" x14ac:dyDescent="0.4">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:13" ht="300" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
         <v>1</v>
       </c>
       <c r="G11">
@@ -1262,17 +1203,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="277" x14ac:dyDescent="0.4">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" ht="275" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
         <v>1</v>
       </c>
       <c r="G12">
@@ -1297,621 +1238,372 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="G13" s="14" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="50" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="25" x14ac:dyDescent="0.3">
+      <c r="D16" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="52" x14ac:dyDescent="0.4">
-      <c r="A15" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="D16" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
+      <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="225" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="200" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="175" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="5" customFormat="1" ht="125" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="227" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="275" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="127" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
+      <c r="B33" s="9"/>
+      <c r="C33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" ht="100" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="202" x14ac:dyDescent="0.4">
-      <c r="A21" s="12" t="s">
+      <c r="B34" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="150" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="177" x14ac:dyDescent="0.4">
-      <c r="A22" s="12" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="4" customFormat="1" ht="127" x14ac:dyDescent="0.4">
-      <c r="A23" s="12" t="s">
+      <c r="C36" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="100" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B37" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" ht="152" x14ac:dyDescent="0.4">
-      <c r="A24" s="12" t="s">
+      <c r="C37" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="152" x14ac:dyDescent="0.4">
-      <c r="A25" s="12" t="s">
+      <c r="B38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="100" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="127" x14ac:dyDescent="0.4">
-      <c r="A26" s="12" t="s">
+      <c r="B39" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="75" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="127" x14ac:dyDescent="0.4">
-      <c r="A27" s="12" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="152" x14ac:dyDescent="0.4">
-      <c r="A28" s="12" t="s">
+      <c r="B41" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="125" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="3" customFormat="1" ht="23" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="230" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="21"/>
-    </row>
-    <row r="34" spans="1:7" ht="140" x14ac:dyDescent="0.4">
-      <c r="A34" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A35" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A36" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A37" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A38" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A39" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A40" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="140" x14ac:dyDescent="0.4">
-      <c r="A41" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="140" x14ac:dyDescent="0.4">
-      <c r="A42" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15" t="s">
+      <c r="B42" s="9"/>
+      <c r="C42" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13D4B0-48A1-0F49-921C-E1EA8DE8A107}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="32" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="6" width="46.83203125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="103.5" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="66" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="27" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
-    </row>
-    <row r="3" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A3" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A6" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="99" x14ac:dyDescent="0.4">
-      <c r="A7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="99" x14ac:dyDescent="0.4">
-      <c r="A8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="99" x14ac:dyDescent="0.4">
-      <c r="A9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="165" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
+++ b/Data/Spreadsheets/subcomponent_scenarios_plus_descriptions.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/Spreadsheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9BDEC2-404C-5C46-BF0E-2BE19622701E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5D0EAD-F621-B64A-8788-C1470781BEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17400" activeTab="1" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
+    <workbookView xWindow="140" yWindow="1540" windowWidth="29260" windowHeight="16100" xr2:uid="{E3CEDC4D-39E8-6049-89E8-D0BEF71875A0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="3 scenerios + descriptions" sheetId="2" r:id="rId1"/>
+    <sheet name="Old drafts" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
   <si>
     <t>Det Value</t>
   </si>
@@ -364,13 +364,50 @@
   </si>
   <si>
     <t>Choose if you think detention harms communities but may reduce crime</t>
+  </si>
+  <si>
+    <t>Long Description</t>
+  </si>
+  <si>
+    <t>WTP</t>
+  </si>
+  <si>
+    <t>RHV</t>
+  </si>
+  <si>
+    <t>Choose if you think detention produces wider community harms beyond what an individual would account for</t>
+  </si>
+  <si>
+    <t>This scenario uses our preferred baseline specification for valuing pretrial detention. Harm to detainees is measured using the Relative Harm Valuation scale, which produces a relatively large negative value per day in custody based on an indirect survey of the general population. We do not add any spillover harms to the detainee’s community as we consider  those may already be captured by the RHV measure. This combination relies on components that are strongly supported in the literature and keeps additional assumptions to a minimum.</t>
+  </si>
+  <si>
+    <t>Focus on broad inclusion and valuation of detainee harms</t>
+  </si>
+  <si>
+    <t>Focus on conservative valuation of detainee harms</t>
+  </si>
+  <si>
+    <t>Most Conservative MVPFs</t>
+  </si>
+  <si>
+    <t>Least Conservative MVPFs</t>
+  </si>
+  <si>
+    <t>In this scenario, harm to detainees is valued using a smaller, survey-based  estimate instead of the larger Relative Harm Valuation scale. The WTP measure treats each day in jail as roughly 300 times less negative than the RHV scale, so the harm attributed to detention is much smaller in magnitude. As a result, the numerator becomes less negative and the MVPF for detention moves closer to zero.</t>
+  </si>
+  <si>
+    <t>Each scenario shows an MVPF for pretrial detention that compares harms and benefits to the public cost of running Cook County Jail in 2018. In every scenario, the numerator includes a negative value for harm to the detained person and a positive value for improved court appearance. The denominator is always total 2018 Cook County Jail funding.
+The three scenarios differ only in how we value harm to detainees (a larger Relative Harm Valuation scale versus a smaller survey-based Willingness to Pay for Freedom) and whether we add an extra negative term for spillover harms to the detainee’s community. In all scenarios, the crime effect components are set to zero by default; they only change if you adjust that parameter elsewhere in the dashboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This scenario uses the same detainee value as the baseline set up (RHV) and adds another value to the numerator that captures some of the potential spillover effects of detention on the community of the detainee that are not already captured by the detainee value. This addition makes the numerator, and the overall MVPF, more negative. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -396,6 +433,20 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -431,65 +482,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="24"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -497,11 +511,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -510,54 +533,39 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -891,32 +899,268 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805EFD8A-C249-BE48-BBB0-37060E53EDE7}">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="27" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="76.5" style="10" customWidth="1"/>
+    <col min="2" max="3" width="31" style="10" customWidth="1"/>
+    <col min="4" max="4" width="41.5" style="10" customWidth="1"/>
+    <col min="5" max="5" width="105.1640625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20.5" style="10" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="10" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="12" customFormat="1" ht="275">
+      <c r="A3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="125">
+      <c r="A4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="175">
+      <c r="A5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="125">
+      <c r="A6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="27" customHeight="1">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+    </row>
+    <row r="14" spans="1:10" s="14" customFormat="1" ht="27" customHeight="1">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="23" spans="1:7" s="13" customFormat="1" ht="27" customHeight="1">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" spans="1:7" ht="27" customHeight="1">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" ht="27" customHeight="1">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="1:7" ht="28" customHeight="1">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="1:7" ht="30" customHeight="1">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="1:7" ht="27" customHeight="1">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE80E8B-CEB2-B84F-9C91-FD8EDADFF9F9}">
   <dimension ref="A1:M43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="34" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="24"/>
   <cols>
-    <col min="1" max="1" width="76.5" style="12" customWidth="1"/>
-    <col min="2" max="2" width="31" style="12" customWidth="1"/>
-    <col min="3" max="3" width="41.5" style="12" customWidth="1"/>
-    <col min="4" max="4" width="57.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="34" style="5" customWidth="1"/>
-    <col min="6" max="6" width="39.1640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="69.6640625" customWidth="1"/>
+    <col min="1" max="1" width="76.5" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="41.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="57.6640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="34" style="10" customWidth="1"/>
+    <col min="6" max="6" width="39.1640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="10" max="10" width="15.83203125" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:13" ht="25">
+      <c r="A1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
@@ -926,19 +1170,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="302" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="300">
+      <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -963,20 +1209,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="202" x14ac:dyDescent="0.4">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:13" ht="200">
+      <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
         <v>0</v>
       </c>
       <c r="G4">
@@ -1001,17 +1247,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="277" x14ac:dyDescent="0.4">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:13" ht="275">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>0</v>
       </c>
       <c r="G5">
@@ -1036,20 +1282,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="327" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:13" ht="325">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
         <v>0</v>
       </c>
       <c r="G6">
@@ -1074,21 +1320,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="202" x14ac:dyDescent="0.4">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:13" ht="200">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
         <v>1</v>
       </c>
       <c r="G7">
@@ -1113,20 +1359,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="202" x14ac:dyDescent="0.4">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:13" ht="200">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="5">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
         <v>1</v>
       </c>
       <c r="G8">
@@ -1151,20 +1397,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="177" x14ac:dyDescent="0.4">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:13" ht="175">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
         <v>1</v>
       </c>
       <c r="G9">
@@ -1189,17 +1435,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="177" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:13" ht="175">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
         <v>1</v>
       </c>
       <c r="G10">
@@ -1224,20 +1470,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="302" x14ac:dyDescent="0.4">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:13" ht="300">
+      <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
         <v>1</v>
       </c>
       <c r="G11">
@@ -1262,17 +1508,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="277" x14ac:dyDescent="0.4">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:13" ht="275">
+      <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
         <v>1</v>
       </c>
       <c r="G12">
@@ -1297,621 +1543,372 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="G13" s="14" t="s">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="50">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="25">
+      <c r="D16" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="52" x14ac:dyDescent="0.4">
-      <c r="A15" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="D16" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
+      <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="225">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="125">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="200">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="175">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="5" customFormat="1" ht="125">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" spans="1:6" ht="150">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="150">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="125">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="125">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="150">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="3" customFormat="1" ht="25">
+      <c r="A32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="227" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="275">
+      <c r="A33" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="127" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
+      <c r="B33" s="9"/>
+      <c r="C33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" ht="100">
+      <c r="A34" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="202" x14ac:dyDescent="0.4">
-      <c r="A21" s="12" t="s">
+      <c r="B34" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="150">
+      <c r="A35" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="177" x14ac:dyDescent="0.4">
-      <c r="A22" s="12" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="125">
+      <c r="A36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="4" customFormat="1" ht="127" x14ac:dyDescent="0.4">
-      <c r="A23" s="12" t="s">
+      <c r="C36" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="100">
+      <c r="A37" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B37" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" ht="152" x14ac:dyDescent="0.4">
-      <c r="A24" s="12" t="s">
+      <c r="C37" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="125">
+      <c r="A38" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="152" x14ac:dyDescent="0.4">
-      <c r="A25" s="12" t="s">
+      <c r="B38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="100">
+      <c r="A39" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="127" x14ac:dyDescent="0.4">
-      <c r="A26" s="12" t="s">
+      <c r="B39" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="75">
+      <c r="A40" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="127" x14ac:dyDescent="0.4">
-      <c r="A27" s="12" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="125">
+      <c r="A41" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="152" x14ac:dyDescent="0.4">
-      <c r="A28" s="12" t="s">
+      <c r="B41" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="125">
+      <c r="A42" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="3" customFormat="1" ht="23" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="230" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="21"/>
-    </row>
-    <row r="34" spans="1:7" ht="140" x14ac:dyDescent="0.4">
-      <c r="A34" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A35" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A36" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A37" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A38" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A39" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="105" x14ac:dyDescent="0.4">
-      <c r="A40" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="140" x14ac:dyDescent="0.4">
-      <c r="A41" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="140" x14ac:dyDescent="0.4">
-      <c r="A42" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15" t="s">
+      <c r="B42" s="9"/>
+      <c r="C42" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
+    <row r="43" spans="1:6">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13D4B0-48A1-0F49-921C-E1EA8DE8A107}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="32" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="6" width="46.83203125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="103.5" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="66" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="27" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
-    </row>
-    <row r="3" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A3" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A6" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="99" x14ac:dyDescent="0.4">
-      <c r="A7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="99" x14ac:dyDescent="0.4">
-      <c r="A8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="99" x14ac:dyDescent="0.4">
-      <c r="A9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="165" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="132" x14ac:dyDescent="0.4">
-      <c r="A11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>